--- a/server-side/modelling/results/cueva svm tables.xlsx
+++ b/server-side/modelling/results/cueva svm tables.xlsx
@@ -7,24 +7,24 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="cueva svm 1 0p1 cm" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="cueva svm 1 0p1 metrics" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="cueva svm 1 0p5 cm" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="cueva svm 1 0p5 metrics" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="cueva svm 1 1 cm" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="cueva svm 1 1 metrics" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="cueva svm 10 0p1 cm" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="cueva svm 10 0p1 metrics" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="cueva svm 10 0p5 cm" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="cueva svm 10 0p5 metrics" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="cueva svm 10 1 cm" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="cueva svm 10 1 metrics" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="cueva svm 100 0p1 cm" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="cueva svm 100 0p1 metrics" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="cueva svm 100 0p5 cm" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="cueva svm 100 0p5 metrics" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="cueva svm 100 1 cm" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="cueva svm 100 1 metrics" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="cueva_second_phase svm 1 0p1 cm" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="cueva_second_phase svm 1 0p1 metrics" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="cueva_second_phase svm 1 0p5 cm" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="cueva_second_phase svm 1 0p5 metrics" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="cueva_second_phase svm 1 1 cm" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="cueva_second_phase svm 1 1 metrics" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="cueva_second_phase svm 10 0p1 cm" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="cueva_second_phase svm 10 0p1 metrics" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="cueva_second_phase svm 10 0p5 cm" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="cueva_second_phase svm 10 0p5 metrics" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="cueva_second_phase svm 10 1 cm" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="cueva_second_phase svm 10 1 metrics" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="cueva_second_phase svm 100 0p1 cm" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="cueva_second_phase svm 100 0p1 metrics" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="cueva_second_phase svm 100 0p5 cm" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="cueva_second_phase svm 100 0p5 metrics" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="cueva_second_phase svm 100 1 cm" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="cueva_second_phase svm 100 1 metrics" sheetId="18" state="visible" r:id="rId18"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/server-side/modelling/results/cueva svm tables.xlsx
+++ b/server-side/modelling/results/cueva svm tables.xlsx
@@ -7,24 +7,24 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="cueva_second_phase svm 1 0p1 cm" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="cueva_second_phase svm 1 0p1 metrics" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="cueva_second_phase svm 1 0p5 cm" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="cueva_second_phase svm 1 0p5 metrics" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="cueva_second_phase svm 1 1 cm" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="cueva_second_phase svm 1 1 metrics" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="cueva_second_phase svm 10 0p1 cm" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="cueva_second_phase svm 10 0p1 metrics" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="cueva_second_phase svm 10 0p5 cm" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="cueva_second_phase svm 10 0p5 metrics" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="cueva_second_phase svm 10 1 cm" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="cueva_second_phase svm 10 1 metrics" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="cueva_second_phase svm 100 0p1 cm" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="cueva_second_phase svm 100 0p1 metrics" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="cueva_second_phase svm 100 0p5 cm" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="cueva_second_phase svm 100 0p5 metrics" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="cueva_second_phase svm 100 1 cm" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="cueva_second_phase svm 100 1 metrics" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="cueva svm 1 0p1 cm" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="cueva svm 1 0p1 metrics" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="cueva svm 1 0p5 cm" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="cueva svm 1 0p5 metrics" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="cueva svm 1 1 cm" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="cueva svm 1 1 metrics" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="cueva svm 10 0p1 cm" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="cueva svm 10 0p1 metrics" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="cueva svm 10 0p5 cm" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="cueva svm 10 0p5 metrics" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="cueva svm 10 1 cm" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="cueva svm 10 1 metrics" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="cueva svm 100 0p1 cm" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="cueva svm 100 0p1 metrics" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="cueva svm 100 0p5 cm" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="cueva svm 100 0p5 metrics" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="cueva svm 100 1 cm" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="cueva svm 100 1 metrics" sheetId="18" state="visible" r:id="rId18"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
